--- a/www/flightdata/xlsx/eoss-355.xlsx
+++ b/www/flightdata/xlsx/eoss-355.xlsx
@@ -3693,7 +3693,7 @@
         <v>33452.41</v>
       </c>
       <c r="I2">
-        <v>731</v>
+        <v>479</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
